--- a/Copy of 0. 131.xlsx
+++ b/Copy of 0. 131.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\.Freelancer\BTTD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC44A6E2-A4D3-48A7-A47C-F6D4F5938D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978D4152-7514-48A5-B5B4-F2235416E02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,6 +417,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -425,9 +428,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1408,28 +1408,28 @@
       <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="24" t="s">
+      <c r="A7" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="F7" s="25"/>
+      <c r="G7" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="24"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="27"/>
       <c r="D10" s="12">
         <f>SUBTOTAL(9,D11:D13)</f>
         <v>1457585643</v>
@@ -1586,27 +1586,27 @@
         <v>22</v>
       </c>
       <c r="C14" s="12">
-        <f>SUBTOTAL(9,C15:C15)</f>
+        <f t="shared" ref="C14:H14" si="0">SUBTOTAL(9,C15:C15)</f>
         <v>13000000</v>
       </c>
       <c r="D14" s="12">
-        <f>SUBTOTAL(9,D15:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14" s="12">
-        <f>SUBTOTAL(9,E15:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14" s="12">
-        <f>SUBTOTAL(9,F15:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14" s="12">
-        <f>SUBTOTAL(9,G15:G15)</f>
+        <f t="shared" si="0"/>
         <v>13000000</v>
       </c>
       <c r="H14" s="13">
-        <f>SUBTOTAL(9,H15:H15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
         <v>25</v>
       </c>
       <c r="C16" s="20">
-        <f>SUBTOTAL(9,C10:C15)</f>
+        <f t="shared" ref="C16:H16" si="1">SUBTOTAL(9,C10:C15)</f>
         <v>13000000</v>
       </c>
       <c r="D16" s="20">
-        <f>SUBTOTAL(9,D10:D15)</f>
+        <f t="shared" si="1"/>
         <v>1457585643</v>
       </c>
       <c r="E16" s="20">
-        <f>SUBTOTAL(9,E10:E15)</f>
+        <f t="shared" si="1"/>
         <v>188802186</v>
       </c>
       <c r="F16" s="20">
-        <f>SUBTOTAL(9,F10:F15)</f>
+        <f t="shared" si="1"/>
         <v>109680000</v>
       </c>
       <c r="G16" s="20">
-        <f>SUBTOTAL(9,G10:G15)</f>
+        <f t="shared" si="1"/>
         <v>13000000</v>
       </c>
       <c r="H16" s="21">
-        <f>SUBTOTAL(9,H10:H15)</f>
+        <f t="shared" si="1"/>
         <v>1378463457</v>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>

--- a/Copy of 0. 131.xlsx
+++ b/Copy of 0. 131.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\.Freelancer\BTTD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978D4152-7514-48A5-B5B4-F2235416E02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026CF244-D0A1-42C9-871F-362CF7F690B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Mã</t>
   </si>
@@ -70,34 +70,10 @@
     <t>Các công ty thuộc Tây Đô Group</t>
   </si>
   <si>
-    <t xml:space="preserve">100001          </t>
-  </si>
-  <si>
-    <t>Công ty Cổ phần Xi Măng Tây Đô</t>
-  </si>
-  <si>
-    <t>100002</t>
-  </si>
-  <si>
-    <t>Công ty Cổ Phần BêTông Tây Đô</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100003          </t>
-  </si>
-  <si>
-    <t>Công ty CP Vận Tải Xi Măng Tây Đô</t>
-  </si>
-  <si>
-    <t>Đơn vị, cá nhân, tổ chức có MST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214580          </t>
-  </si>
-  <si>
-    <t>CÔNG TY TNHH THƯƠNG MẠI XÂY DỰNG VÀ DU LỊCH AN PHÚC</t>
-  </si>
-  <si>
     <t>Tổng cộng:</t>
+  </si>
+  <si>
+    <t>abcdrf</t>
   </si>
 </sst>
 </file>
@@ -346,7 +322,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -378,45 +354,45 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -425,9 +401,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -836,13 +809,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -860,7 +833,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="3219450"/>
+          <a:off x="0" y="2305050"/>
           <a:ext cx="10217150" cy="463550"/>
           <a:chOff x="0" y="11420"/>
           <a:chExt cx="1023" cy="49"/>
@@ -1378,7 +1351,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1477,220 +1450,112 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="12">
-        <f>SUBTOTAL(9,D11:D13)</f>
-        <v>1457585643</v>
-      </c>
-      <c r="E10" s="12">
-        <f>SUBTOTAL(9,E11:E13)</f>
-        <v>188802186</v>
-      </c>
-      <c r="F10" s="12">
-        <f>SUBTOTAL(9,F11:F13)</f>
-        <v>109680000</v>
-      </c>
-      <c r="G10" s="12">
-        <f>SUBTOTAL(9,G11:G13)</f>
+      <c r="C10" s="23"/>
+      <c r="D10" s="11">
+        <f>SUBTOTAL(9,D11:D11)</f>
+        <v>1457185643</v>
+      </c>
+      <c r="E10" s="11">
+        <f>SUBTOTAL(9,E11:E11)</f>
+        <v>113202186</v>
+      </c>
+      <c r="F10" s="11">
+        <f>SUBTOTAL(9,F11:F11)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="13">
-        <f>SUBTOTAL(9,H11:H13)</f>
-        <v>1378463457</v>
+      <c r="G10" s="11">
+        <f>SUBTOTAL(9,G11:G11)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <f>SUBTOTAL(9,H11:H11)</f>
+        <v>1343983457</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13">
+        <v>192111</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1457185643</v>
+      </c>
+      <c r="E11" s="15">
+        <v>113202186</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <v>1343983457</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="16">
+      <c r="C12" s="19">
+        <f>SUBTOTAL(9,C10:C11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D12" s="19">
+        <f>SUBTOTAL(9,D10:D11)</f>
         <v>1457185643</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E12" s="19">
+        <f>SUBTOTAL(9,E10:E11)</f>
         <v>113202186</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F12" s="19">
+        <f>SUBTOTAL(9,F10:F11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G12" s="19">
+        <f>SUBTOTAL(9,G10:G11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H12" s="20">
+        <f>SUBTOTAL(9,H10:H11)</f>
         <v>1343983457</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="16">
-        <v>0</v>
-      </c>
-      <c r="D12" s="16">
-        <v>400000</v>
-      </c>
-      <c r="E12" s="16">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16">
-        <v>34080000</v>
-      </c>
-      <c r="G12" s="16">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>34480000</v>
-      </c>
+    <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="16">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>75600000</v>
-      </c>
-      <c r="F13" s="16">
-        <v>75600000</v>
-      </c>
-      <c r="G13" s="16">
-        <v>0</v>
-      </c>
-      <c r="H13" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="12">
-        <f t="shared" ref="C14:H14" si="0">SUBTOTAL(9,C15:C15)</f>
-        <v>13000000</v>
-      </c>
-      <c r="D14" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <f t="shared" si="0"/>
-        <v>13000000</v>
-      </c>
-      <c r="H14" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="25.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="16">
-        <v>13000000</v>
-      </c>
-      <c r="D15" s="16">
-        <v>0</v>
-      </c>
-      <c r="E15" s="16">
-        <v>0</v>
-      </c>
-      <c r="F15" s="16">
-        <v>0</v>
-      </c>
-      <c r="G15" s="16">
-        <v>13000000</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="20">
-        <f t="shared" ref="C16:H16" si="1">SUBTOTAL(9,C10:C15)</f>
-        <v>13000000</v>
-      </c>
-      <c r="D16" s="20">
-        <f t="shared" si="1"/>
-        <v>1457585643</v>
-      </c>
-      <c r="E16" s="20">
-        <f t="shared" si="1"/>
-        <v>188802186</v>
-      </c>
-      <c r="F16" s="20">
-        <f t="shared" si="1"/>
-        <v>109680000</v>
-      </c>
-      <c r="G16" s="20">
-        <f t="shared" si="1"/>
-        <v>13000000</v>
-      </c>
-      <c r="H16" s="21">
-        <f t="shared" si="1"/>
-        <v>1378463457</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-    </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="4"/>
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I15 A16:I19" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I10 A12:I15 C11:I11" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Copy of 0. 131.xlsx
+++ b/Copy of 0. 131.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\.Freelancer\BTTD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026CF244-D0A1-42C9-871F-362CF7F690B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C929693-A6C9-45C8-A714-DC0D614321CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
     <t>Tổng cộng:</t>
   </si>
   <si>
-    <t>abcdrf</t>
+    <t>uuuuuu</t>
   </si>
 </sst>
 </file>
@@ -390,6 +390,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -397,9 +400,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1381,28 +1381,28 @@
       <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25" t="s">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="26" t="s">
+      <c r="F7" s="26"/>
+      <c r="G7" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="11">
         <f>SUBTOTAL(9,D11:D11)</f>
         <v>1457185643</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
-        <v>192111</v>
+        <v>196381</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>17</v>
@@ -1507,27 +1507,27 @@
         <v>16</v>
       </c>
       <c r="C12" s="19">
-        <f>SUBTOTAL(9,C10:C11)</f>
+        <f t="shared" ref="C12:H12" si="0">SUBTOTAL(9,C10:C11)</f>
         <v>0</v>
       </c>
       <c r="D12" s="19">
-        <f>SUBTOTAL(9,D10:D11)</f>
+        <f t="shared" si="0"/>
         <v>1457185643</v>
       </c>
       <c r="E12" s="19">
-        <f>SUBTOTAL(9,E10:E11)</f>
+        <f t="shared" si="0"/>
         <v>113202186</v>
       </c>
       <c r="F12" s="19">
-        <f>SUBTOTAL(9,F10:F11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G12" s="19">
-        <f>SUBTOTAL(9,G10:G11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H12" s="20">
-        <f>SUBTOTAL(9,H10:H11)</f>
+        <f t="shared" si="0"/>
         <v>1343983457</v>
       </c>
     </row>

--- a/Copy of 0. 131.xlsx
+++ b/Copy of 0. 131.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\.Freelancer\BTTD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C929693-A6C9-45C8-A714-DC0D614321CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55FF55D-216A-4A16-BC47-B2C327F87377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
     <t>Tổng cộng:</t>
   </si>
   <si>
-    <t>uuuuuu</t>
+    <t>wwwwwww</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
-        <v>196381</v>
+        <v>132341</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>17</v>

--- a/Copy of 0. 131.xlsx
+++ b/Copy of 0. 131.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\.Freelancer\BTTD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55FF55D-216A-4A16-BC47-B2C327F87377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C48CD8F-14AC-44C4-941F-AFF69605207B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
     <t>Tổng cộng:</t>
   </si>
   <si>
-    <t>wwwwwww</t>
+    <t>qwerty</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
-        <v>132341</v>
+        <v>132304</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>17</v>
